--- a/LHTRPG_特技データベース.xlsx
+++ b/LHTRPG_特技データベース.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d1807dd80cee582b/ドキュメント/TRPG/01_ログ・ホライズン/ccfolia_駒作成/web_App/lhtrpg_webapp_challenge/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\K.Housako\dev\lhtrpg_webapp_challenge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="352" documentId="13_ncr:1_{D01FCBC1-F906-4A52-AA69-13C1C66C6654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF0A80EE-1299-492C-9B49-F44187F0BAA1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79CDADAF-73D9-49EC-9C62-5EACF4EA59FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="16845" windowHeight="15585" activeTab="1" xr2:uid="{FDD5F9F6-F4A1-4061-854F-C0E163898CC3}"/>
+    <workbookView xWindow="27240" yWindow="-1160" windowWidth="11250" windowHeight="11370" activeTab="1" xr2:uid="{FDD5F9F6-F4A1-4061-854F-C0E163898CC3}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15506" uniqueCount="2490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15506" uniqueCount="2492">
   <si>
     <t>LHTRPG 特技データベース</t>
   </si>
@@ -7522,6 +7522,14 @@
   </si>
   <si>
     <t>ＣＲ１１以上で取得可能。［【攻撃力】＋２Ｄ］の物理ダメージをあたえる。〔判定成功〕対象に［弱点（物理ダメージ）：１０］を与える。この［弱点］はＢＳとして扱う。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>a</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>a</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -7619,14 +7627,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -7664,7 +7668,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -7770,7 +7774,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -7912,7 +7916,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -27748,7 +27752,7 @@
         <v>486</v>
       </c>
       <c r="P408" s="2" t="s">
-        <v>486</v>
+        <v>2490</v>
       </c>
       <c r="Q408" s="1" t="s">
         <v>487</v>
@@ -27795,7 +27799,7 @@
         <v>594</v>
       </c>
       <c r="P409" s="2" t="s">
-        <v>594</v>
+        <v>2490</v>
       </c>
       <c r="Q409" s="1" t="s">
         <v>595</v>
@@ -27842,7 +27846,7 @@
         <v>860</v>
       </c>
       <c r="P410" s="2" t="s">
-        <v>860</v>
+        <v>2491</v>
       </c>
       <c r="Q410" s="1" t="s">
         <v>861</v>
@@ -28042,13 +28046,13 @@
         <v>317</v>
       </c>
       <c r="P414" s="2" t="s">
-        <v>317</v>
+        <v>2491</v>
       </c>
       <c r="Q414" s="1" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="415" spans="1:17" ht="94.5">
+    <row r="415" spans="1:17" ht="78.75">
       <c r="A415" s="1">
         <v>3226</v>
       </c>
@@ -28089,7 +28093,7 @@
         <v>2011</v>
       </c>
       <c r="P415" s="2" t="s">
-        <v>2011</v>
+        <v>2491</v>
       </c>
       <c r="Q415" s="1" t="s">
         <v>2012</v>
@@ -28136,7 +28140,7 @@
         <v>796</v>
       </c>
       <c r="P416" s="2" t="s">
-        <v>796</v>
+        <v>2491</v>
       </c>
       <c r="Q416" s="1" t="s">
         <v>797</v>
@@ -28183,7 +28187,7 @@
         <v>799</v>
       </c>
       <c r="P417" s="2" t="s">
-        <v>799</v>
+        <v>2491</v>
       </c>
       <c r="Q417" s="1" t="s">
         <v>800</v>
@@ -28280,7 +28284,7 @@
         <v>1265</v>
       </c>
       <c r="P419" s="2" t="s">
-        <v>1265</v>
+        <v>2491</v>
       </c>
       <c r="Q419" s="1" t="s">
         <v>1266</v>
@@ -28327,7 +28331,7 @@
         <v>955</v>
       </c>
       <c r="P420" s="2" t="s">
-        <v>955</v>
+        <v>2491</v>
       </c>
       <c r="Q420" s="1" t="s">
         <v>956</v>
@@ -28421,13 +28425,13 @@
         <v>1813</v>
       </c>
       <c r="P422" s="2" t="s">
-        <v>1813</v>
+        <v>2491</v>
       </c>
       <c r="Q422" s="1" t="s">
         <v>1814</v>
       </c>
     </row>
-    <row r="423" spans="1:17" ht="63">
+    <row r="423" spans="1:17" ht="47.25">
       <c r="A423" s="1">
         <v>3301</v>
       </c>
@@ -28471,7 +28475,7 @@
         <v>679</v>
       </c>
       <c r="P423" s="2" t="s">
-        <v>679</v>
+        <v>2491</v>
       </c>
       <c r="Q423" s="1" t="s">
         <v>680</v>
@@ -28518,7 +28522,7 @@
         <v>2205</v>
       </c>
       <c r="P424" s="2" t="s">
-        <v>2205</v>
+        <v>2491</v>
       </c>
       <c r="Q424" s="1" t="s">
         <v>2206</v>
@@ -28565,7 +28569,7 @@
         <v>168</v>
       </c>
       <c r="P425" s="2" t="s">
-        <v>168</v>
+        <v>2491</v>
       </c>
       <c r="Q425" s="1" t="s">
         <v>169</v>
@@ -28612,7 +28616,7 @@
         <v>381</v>
       </c>
       <c r="P426" s="2" t="s">
-        <v>381</v>
+        <v>2491</v>
       </c>
       <c r="Q426" s="1" t="s">
         <v>382</v>
@@ -28662,7 +28666,7 @@
         <v>676</v>
       </c>
       <c r="P427" s="2" t="s">
-        <v>676</v>
+        <v>2491</v>
       </c>
       <c r="Q427" s="1" t="s">
         <v>677</v>
@@ -28709,7 +28713,7 @@
         <v>372</v>
       </c>
       <c r="P428" s="2" t="s">
-        <v>372</v>
+        <v>2491</v>
       </c>
       <c r="Q428" s="1" t="s">
         <v>373</v>
@@ -28856,7 +28860,7 @@
         <v>693</v>
       </c>
       <c r="P431" s="2" t="s">
-        <v>693</v>
+        <v>2491</v>
       </c>
       <c r="Q431" s="1" t="s">
         <v>694</v>
@@ -28906,7 +28910,7 @@
         <v>740</v>
       </c>
       <c r="P432" s="2" t="s">
-        <v>740</v>
+        <v>2491</v>
       </c>
       <c r="Q432" s="1" t="s">
         <v>741</v>
@@ -28953,7 +28957,7 @@
         <v>757</v>
       </c>
       <c r="P433" s="2" t="s">
-        <v>757</v>
+        <v>2491</v>
       </c>
       <c r="Q433" s="1" t="s">
         <v>758</v>
@@ -29000,13 +29004,13 @@
         <v>863</v>
       </c>
       <c r="P434" s="2" t="s">
-        <v>863</v>
+        <v>2491</v>
       </c>
       <c r="Q434" s="1" t="s">
         <v>864</v>
       </c>
     </row>
-    <row r="435" spans="1:17" ht="47.25">
+    <row r="435" spans="1:17" ht="31.5">
       <c r="A435" s="1">
         <v>3408</v>
       </c>
@@ -29047,7 +29051,7 @@
         <v>2050</v>
       </c>
       <c r="P435" s="2" t="s">
-        <v>2050</v>
+        <v>2491</v>
       </c>
       <c r="Q435" s="1" t="s">
         <v>2051</v>
